--- a/artfynd/A 64324-2023 artfynd.xlsx
+++ b/artfynd/A 64324-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120376876</v>
+        <v>120376895</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>94454</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -778,12 +779,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Wood surface of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120376819</v>
+        <v>120376825</v>
       </c>
       <c r="B3" t="n">
-        <v>105032</v>
+        <v>94550</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,31 +818,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -901,6 +902,26 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Picea abies</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -916,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120376825</v>
+        <v>120376876</v>
       </c>
       <c r="B4" t="n">
-        <v>94550</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,39 +949,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -968,10 +980,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617234</v>
+        <v>617157</v>
       </c>
       <c r="R4" t="n">
-        <v>6558711</v>
+        <v>6558818</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1028,12 +1040,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Picea abies</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1051,10 +1063,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120376879</v>
+        <v>120376819</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>105032</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1063,30 +1075,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1094,10 +1115,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617157</v>
+        <v>617234</v>
       </c>
       <c r="R5" t="n">
-        <v>6558818</v>
+        <v>6558711</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1157,10 +1178,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120376895</v>
+        <v>120376879</v>
       </c>
       <c r="B6" t="n">
-        <v>94454</v>
+        <v>91881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,31 +1190,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2818</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1248,26 +1268,6 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 64324-2023 artfynd.xlsx
+++ b/artfynd/A 64324-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120376895</v>
+        <v>120376819</v>
       </c>
       <c r="B2" t="n">
-        <v>94454</v>
+        <v>105032</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,25 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -719,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617157</v>
+        <v>617234</v>
       </c>
       <c r="R2" t="n">
-        <v>6558818</v>
+        <v>6558711</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -766,26 +774,6 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -1063,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120376819</v>
+        <v>120376879</v>
       </c>
       <c r="B5" t="n">
-        <v>105032</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1075,39 +1063,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1115,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617234</v>
+        <v>617157</v>
       </c>
       <c r="R5" t="n">
-        <v>6558711</v>
+        <v>6558818</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1178,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120376879</v>
+        <v>120376895</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>94454</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1190,30 +1169,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>2818</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1268,6 +1248,26 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 64324-2023 artfynd.xlsx
+++ b/artfynd/A 64324-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120376819</v>
+        <v>120376825</v>
       </c>
       <c r="B2" t="n">
-        <v>105032</v>
+        <v>94550</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -775,6 +775,26 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Picea abies</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -790,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120376825</v>
+        <v>120376895</v>
       </c>
       <c r="B3" t="n">
-        <v>94550</v>
+        <v>94454</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,33 +826,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -842,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617234</v>
+        <v>617157</v>
       </c>
       <c r="R3" t="n">
-        <v>6558711</v>
+        <v>6558818</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -925,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120376876</v>
+        <v>120376819</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>105032</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,30 +949,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -968,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617157</v>
+        <v>617234</v>
       </c>
       <c r="R4" t="n">
-        <v>6558818</v>
+        <v>6558711</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1015,26 +1036,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1051,10 +1052,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120376879</v>
+        <v>120376876</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,21 +1068,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1142,6 +1143,26 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1157,10 +1178,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120376895</v>
+        <v>120376879</v>
       </c>
       <c r="B6" t="n">
-        <v>94454</v>
+        <v>91881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,31 +1190,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2818</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1248,26 +1268,6 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 64324-2023 artfynd.xlsx
+++ b/artfynd/A 64324-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120376825</v>
+        <v>120376819</v>
       </c>
       <c r="B2" t="n">
-        <v>94550</v>
+        <v>105032</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -775,26 +775,6 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Picea abies</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -810,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120376895</v>
+        <v>120376879</v>
       </c>
       <c r="B3" t="n">
-        <v>94454</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,31 +802,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -901,26 +880,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -937,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120376819</v>
+        <v>120376876</v>
       </c>
       <c r="B4" t="n">
-        <v>105032</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,39 +908,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -989,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617234</v>
+        <v>617157</v>
       </c>
       <c r="R4" t="n">
-        <v>6558711</v>
+        <v>6558818</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1036,6 +986,26 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1052,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120376876</v>
+        <v>120376895</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>94454</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,30 +1034,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1155,12 +1126,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Wood surface of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1178,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120376879</v>
+        <v>120376825</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>94550</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1190,30 +1161,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1221,10 +1201,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>617157</v>
+        <v>617234</v>
       </c>
       <c r="R6" t="n">
-        <v>6558818</v>
+        <v>6558711</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1268,6 +1248,26 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 64324-2023 artfynd.xlsx
+++ b/artfynd/A 64324-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120376819</v>
+        <v>120376876</v>
       </c>
       <c r="B2" t="n">
-        <v>105032</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617234</v>
+        <v>617157</v>
       </c>
       <c r="R2" t="n">
-        <v>6558711</v>
+        <v>6558818</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -774,6 +765,26 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -790,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120376879</v>
+        <v>120376825</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>94550</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,30 +813,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617157</v>
+        <v>617234</v>
       </c>
       <c r="R3" t="n">
-        <v>6558818</v>
+        <v>6558711</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,6 +900,26 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -896,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120376876</v>
+        <v>120376819</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>105032</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,30 +948,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +988,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617157</v>
+        <v>617234</v>
       </c>
       <c r="R4" t="n">
-        <v>6558818</v>
+        <v>6558711</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,26 +1035,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1149,10 +1178,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120376825</v>
+        <v>120376879</v>
       </c>
       <c r="B6" t="n">
-        <v>94550</v>
+        <v>91881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,39 +1190,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1201,10 +1221,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>617234</v>
+        <v>617157</v>
       </c>
       <c r="R6" t="n">
-        <v>6558711</v>
+        <v>6558818</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1248,26 +1268,6 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 64324-2023 artfynd.xlsx
+++ b/artfynd/A 64324-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120376876</v>
+        <v>120376825</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>94550</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617157</v>
+        <v>617234</v>
       </c>
       <c r="R2" t="n">
-        <v>6558818</v>
+        <v>6558711</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -778,12 +787,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Picea abies</t>
+          <t>Wood surface of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120376825</v>
+        <v>120376876</v>
       </c>
       <c r="B3" t="n">
-        <v>94550</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,39 +822,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617234</v>
+        <v>617157</v>
       </c>
       <c r="R3" t="n">
-        <v>6558711</v>
+        <v>6558818</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -913,12 +913,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Vedyta på död ved</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Picea abies</t>
+          <t>Bark of dead wood # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
